--- a/bb-dcf/BB_DCF_Model.xlsx
+++ b/bb-dcf/BB_DCF_Model.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Model" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Operating Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DCF" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -266,20 +266,23 @@
     <xf numFmtId="164" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,9 +292,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -723,17 +723,16 @@
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>DCF!$C$44</f>
+        <f>DCF!$C$48</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>DCF!$C$46</f>
-        <v/>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>OVERWEIGHT</t>
-        </is>
+        <f>DCF!$C$50</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>DCF!$C$51</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -781,7 +780,7 @@
         </is>
       </c>
       <c r="E11" s="10">
-        <f>(Assumptions!$C$42*Assumptions!$C$43-Assumptions!$C$41)/1000</f>
+        <f>(Assumptions!$C$42*Assumptions!$C$43-Assumptions!$C$41+Assumptions!$C$44)/1000</f>
         <v/>
       </c>
     </row>
@@ -802,7 +801,7 @@
         </is>
       </c>
       <c r="E12" s="10">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$41-Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
@@ -833,42 +832,38 @@
           <t>FY2026A Revenue ($M)</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C14" s="10">
+        <f>'Operating Model'!$C$8</f>
+        <v/>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>FY2026A Adj EBITDA ($M)</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E14" s="10">
+        <f>'Operating Model'!$C$12</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>QNX Royalty Backlog</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>$950M</t>
-        </is>
+          <t>QNX Royalty Backlog ($M)</t>
+        </is>
+      </c>
+      <c r="C15" s="10">
+        <f>Assumptions!$C$55</f>
+        <v/>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>FCF (FY2026A)</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>$46.5M</t>
-        </is>
+          <t>FCF (FY2026A, $M)</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>Assumptions!$C$56</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
@@ -916,7 +911,7 @@
     <row r="25" ht="52" customHeight="1">
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Wall Street consensus PT: $4.84 (Hold, 7 analysts). Stock is trading at $5.50, already through consensus — and NVIDIA deal was announced April 20 with no subsequent PT revisions captured in the consensus. Our blended DCF + comps PT of $7.00 reflects QNX's deserved premium as a pure-play safety OS (8x FY2028E EV/Rev for QNX segment vs. a blended 5x being implied by current price). The multiple re-rating is the catalyst.</t>
+          <t>Wall Street consensus PT: $4.84 (Hold, 7 analysts). Stock is trading at $5.50, already through consensus — and NVIDIA deal was announced April 20 with no subsequent PT revisions captured in the consensus. Our blended DCF + comps PT reflects QNX's deserved premium as a pure-play safety OS (8x FY2028E EV/Rev for QNX segment vs. a blended 5x being implied by current price). The multiple re-rating is the catalyst.</t>
         </is>
       </c>
     </row>
@@ -930,7 +925,7 @@
     <row r="28" ht="52" customHeight="1">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>FY2026A FCF of $46.5M (up 3× YoY from $16.5M) and $432M net cash fund a $60M+ buyback program already underway (15.5M shares repurchased). At current share count, FCF yield is ~2.5% and growing to 5%+ by FY2028E as QNX royalties scale. The company returned to GAAP profitability in FY2026 ($53.2M net income), eliminating a major overhang that kept institutional investors sidelined.</t>
+          <t>FY2026A FCF of $46.5M (up 3× YoY from $16.5M) and $432M of cash ($232M net of the $200M convertible) fund a $60M+ buyback program already underway (15.5M shares repurchased). At current share count, FCF yield is ~2.5% and growing to 5%+ by FY2028E as QNX royalties scale. The company returned to GAAP profitability in FY2026 ($53.2M net income), eliminating a major overhang that kept institutional investors sidelined.</t>
         </is>
       </c>
     </row>
@@ -966,13 +961,12 @@
       <c r="G32" s="3" t="inlineStr"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>DCF  (WACC 9.0%, 16× FY2031E EBITDA)</t>
-        </is>
+      <c r="B33" s="12">
+        <f>"DCF  (WACC "&amp;TEXT(Assumptions!$C$23,"0.0%")&amp;", "&amp;TEXT(Assumptions!$C$26,"0")&amp;"× FY2031E EBITDA)"</f>
+        <v/>
       </c>
       <c r="C33" s="13">
-        <f>DCF!$C$28</f>
+        <f>DCF!$C$29</f>
         <v/>
       </c>
       <c r="D33" s="14">
@@ -981,13 +975,12 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>Segment Comps  (QNX 8× / CySec 3.5× FY2028E Rev)</t>
-        </is>
+      <c r="B34" s="12">
+        <f>"Segment Comps  (QNX "&amp;TEXT(Assumptions!$C$29,"0.0")&amp;"× / CySec "&amp;TEXT(Assumptions!$C$30,"0.0")&amp;"× FY2028E Rev, PV)"</f>
+        <v/>
       </c>
       <c r="C34" s="13">
-        <f>DCF!$C$39</f>
+        <f>DCF!$C$43</f>
         <v/>
       </c>
       <c r="D34" s="14">
@@ -1002,7 +995,7 @@
         </is>
       </c>
       <c r="C35" s="5">
-        <f>DCF!$C$44</f>
+        <f>DCF!$C$48</f>
         <v/>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -1041,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H43"/>
+  <dimension ref="B1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1547,14 +1540,190 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Total Debt — 3.00% Convertible Notes ($M)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>$200M principal due Feb 15, 2029 (FY2026A 10-K) — subtracted in both equity bridges</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Years to Discount FY2028E Comps EV</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>FY2028E multiple implies value ~1 year out — discounted back at base WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>QNX EV / Revenue Multiple — Bear</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Scenario summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>QNX EV / Revenue Multiple — Bull</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Scenario summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>SENSITIVITY, RATING &amp; COVER INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Sensitivity Step — WACC</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Axis centred on base WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Sensitivity Step — Exit EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Axis centred on base exit multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Sensitivity Step — QNX EV/Revenue</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Axis centred on base QNX multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Overweight if upside ≥</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D53" s="20" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Underweight if upside ≤</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>Otherwise Equal-Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>QNX Royalty Backlog ($M)</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>950</v>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>FY2026A exit (Q4 FY2026 call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>FY2026A Free Cash Flow ($M)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>FY2026A 10-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Francisco Rodriguez  |  Financial Modeling Portfolio  |  github.com/Azyo1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
@@ -2193,7 +2362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2293,20 +2462,25 @@
           <t>Discount Period  (n)</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="31" t="n">
-        <v>5</v>
+      <c r="D10" s="31">
+        <f>1</f>
+        <v/>
+      </c>
+      <c r="E10" s="31">
+        <f>D10+1</f>
+        <v/>
+      </c>
+      <c r="F10" s="31">
+        <f>E10+1</f>
+        <v/>
+      </c>
+      <c r="G10" s="31">
+        <f>F10+1</f>
+        <v/>
+      </c>
+      <c r="H10" s="31">
+        <f>G10+1</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2316,23 +2490,23 @@
         </is>
       </c>
       <c r="D11" s="32">
-        <f>1/(1+Assumptions!$C$23)^1</f>
+        <f>1/(1+Assumptions!$C$23)^D10</f>
         <v/>
       </c>
       <c r="E11" s="32">
-        <f>1/(1+Assumptions!$C$23)^2</f>
+        <f>1/(1+Assumptions!$C$23)^E10</f>
         <v/>
       </c>
       <c r="F11" s="32">
-        <f>1/(1+Assumptions!$C$23)^3</f>
+        <f>1/(1+Assumptions!$C$23)^F10</f>
         <v/>
       </c>
       <c r="G11" s="32">
-        <f>1/(1+Assumptions!$C$23)^4</f>
+        <f>1/(1+Assumptions!$C$23)^G10</f>
         <v/>
       </c>
       <c r="H11" s="32">
-        <f>1/(1+Assumptions!$C$23)^5</f>
+        <f>1/(1+Assumptions!$C$23)^H10</f>
         <v/>
       </c>
     </row>
@@ -2421,7 +2595,7 @@
         </is>
       </c>
       <c r="C19" s="28">
-        <f>C18/(1+Assumptions!$C$23)^5</f>
+        <f>C18*H11</f>
         <v/>
       </c>
     </row>
@@ -2477,213 +2651,268 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>(–) Convertible Notes  ($M)</t>
+        </is>
+      </c>
+      <c r="C26" s="24">
+        <f>Assumptions!$C$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Equity Value  ($M)</t>
         </is>
       </c>
-      <c r="C26" s="28">
-        <f>C24+C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="C27" s="28">
+        <f>C24+C25-C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>(÷) Shares Outstanding  (M)</t>
         </is>
       </c>
-      <c r="C27" s="24">
+      <c r="C28" s="24">
         <f>Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>DCF Price Target  ($/share)</t>
         </is>
       </c>
-      <c r="C28" s="34">
-        <f>C26/C27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="8" t="inlineStr">
+      <c r="C29" s="34">
+        <f>C27/C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>SEGMENT COMPS  (FY2028E EV / REVENUE)</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>IoT / QNX Revenue  (FY2028E, $M)</t>
-        </is>
-      </c>
-      <c r="C31" s="24">
-        <f>'Operating Model'!$E$4</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>× QNX EV/Revenue Multiple</t>
+          <t>IoT / QNX Revenue  (FY2028E, $M)</t>
         </is>
       </c>
       <c r="C32" s="24">
-        <f>C31*Assumptions!$C$29</f>
+        <f>'Operating Model'!$E$4</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Cybersecurity Revenue  (FY2028E, $M)</t>
+          <t>× QNX EV/Revenue Multiple</t>
         </is>
       </c>
       <c r="C33" s="24">
-        <f>'Operating Model'!$E$6</f>
+        <f>C32*Assumptions!$C$29</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="12" t="inlineStr">
         <is>
+          <t>Cybersecurity Revenue  (FY2028E, $M)</t>
+        </is>
+      </c>
+      <c r="C34" s="24">
+        <f>'Operating Model'!$E$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
           <t>× CySec EV/Revenue Multiple</t>
         </is>
       </c>
-      <c r="C34" s="24">
-        <f>C33*Assumptions!$C$30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Total Segment EV  ($M)</t>
-        </is>
-      </c>
-      <c r="C35" s="28">
-        <f>C32+C34</f>
+      <c r="C35" s="24">
+        <f>C34*Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="12" t="inlineStr">
         <is>
+          <t>Segment EV — FY2028E basis  ($M)</t>
+        </is>
+      </c>
+      <c r="C36" s="24">
+        <f>C33+C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>× Discount Factor  [1/(1+WACC)^years]</t>
+        </is>
+      </c>
+      <c r="C37" s="35">
+        <f>1/(1+Assumptions!$C$23)^Assumptions!$C$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Total Segment EV — Present Value  ($M)</t>
+        </is>
+      </c>
+      <c r="C38" s="28">
+        <f>C36*C37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="12" t="inlineStr">
+        <is>
           <t>(+) Cash &amp; Investments  ($M)</t>
         </is>
       </c>
-      <c r="C36" s="24">
+      <c r="C39" s="24">
         <f>Assumptions!$C$41</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>(–) Convertible Notes  ($M)</t>
+        </is>
+      </c>
+      <c r="C40" s="24">
+        <f>Assumptions!$C$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Equity Value  ($M)</t>
         </is>
       </c>
-      <c r="C37" s="28">
-        <f>C35+C36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>(÷) Shares Outstanding  (M)</t>
-        </is>
-      </c>
-      <c r="C38" s="24">
-        <f>Assumptions!$C$42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Comps Price Target  ($/share)</t>
-        </is>
-      </c>
-      <c r="C39" s="34">
-        <f>C37/C38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>BLENDED PRICE TARGET</t>
-        </is>
+      <c r="C41" s="28">
+        <f>C38+C39-C40</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="12" t="inlineStr">
         <is>
+          <t>(÷) Shares Outstanding  (M)</t>
+        </is>
+      </c>
+      <c r="C42" s="24">
+        <f>Assumptions!$C$42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Comps Price Target  ($/share)</t>
+        </is>
+      </c>
+      <c r="C43" s="34">
+        <f>C41/C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>BLENDED PRICE TARGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="12" t="inlineStr">
+        <is>
           <t>DCF Weight</t>
         </is>
       </c>
-      <c r="C42" s="30">
+      <c r="C46" s="30">
         <f>Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="12" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Comps Weight</t>
         </is>
       </c>
-      <c r="C43" s="30">
+      <c r="C47" s="30">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>★  BLENDED PRICE TARGET  ($/share)</t>
         </is>
       </c>
-      <c r="C44" s="34">
-        <f>C42*C28+C43*C39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="12" t="inlineStr">
+      <c r="C48" s="34">
+        <f>C46*C29+C47*C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Current Stock Price</t>
         </is>
       </c>
-      <c r="C45" s="35">
+      <c r="C49" s="36">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="4" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Upside / (Downside)</t>
         </is>
       </c>
-      <c r="C46" s="36">
-        <f>(C44-C45)/C45</f>
+      <c r="C50" s="37">
+        <f>(C48-C49)/C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>★  RATING</t>
+        </is>
+      </c>
+      <c r="C51" s="38">
+        <f>IF(C50&gt;=Assumptions!$C$53,"OVERWEIGHT",IF(C50&lt;=Assumptions!$C$54,"UNDERWEIGHT","EQUAL-WEIGHT"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B45:E45"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B3:E3"/>
   </mergeCells>
@@ -2728,336 +2957,352 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>WACC ↓ | Exit Mult →</t>
         </is>
       </c>
-      <c r="C4" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" s="38" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="38" t="n">
-        <v>14</v>
-      </c>
-      <c r="F4" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="G4" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="H4" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="I4" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="J4" s="38" t="n">
-        <v>24</v>
+      <c r="C4" s="40">
+        <f>Assumptions!$C$26+(-3)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="D4" s="40">
+        <f>Assumptions!$C$26+(-2)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="E4" s="40">
+        <f>Assumptions!$C$26+(-1)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="F4" s="40">
+        <f>Assumptions!$C$26+(0)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="G4" s="40">
+        <f>Assumptions!$C$26+(1)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="H4" s="40">
+        <f>Assumptions!$C$26+(2)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="I4" s="40">
+        <f>Assumptions!$C$26+(3)*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="J4" s="40">
+        <f>Assumptions!$C$26+(4)*Assumptions!$C$51</f>
+        <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="39" t="n">
-        <v>0.075</v>
+      <c r="B5" s="22">
+        <f>Assumptions!$C$23+(-3)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*C$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*C$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*D$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*D$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*E$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*E$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*F$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*F$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*G$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*G$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*H$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*H$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*I$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*I$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J5" s="13">
-        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*J$4/(1+$B5)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B5)^1+'Operating Model'!$E$24/(1+$B5)^2+'Operating Model'!$F$24/(1+$B5)^3+'Operating Model'!$G$24/(1+$B5)^4+'Operating Model'!$H$24/(1+$B5)^5+'Operating Model'!$H$12*J$4/(1+$B5)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="B6" s="39" t="n">
-        <v>0.08</v>
+      <c r="B6" s="22">
+        <f>Assumptions!$C$23+(-2)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*C$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*C$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*D$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*D$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*E$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*E$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*F$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*F$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*G$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*G$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*H$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*H$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*I$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*I$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J6" s="13">
-        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*J$4/(1+$B6)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B6)^1+'Operating Model'!$E$24/(1+$B6)^2+'Operating Model'!$F$24/(1+$B6)^3+'Operating Model'!$G$24/(1+$B6)^4+'Operating Model'!$H$24/(1+$B6)^5+'Operating Model'!$H$12*J$4/(1+$B6)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="39" t="n">
-        <v>0.08500000000000001</v>
+      <c r="B7" s="22">
+        <f>Assumptions!$C$23+(-1)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*C$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*C$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*D$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*D$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*E$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*E$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*F$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*F$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*G$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*G$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*H$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*H$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*I$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*I$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J7" s="13">
-        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*J$4/(1+$B7)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B7)^1+'Operating Model'!$E$24/(1+$B7)^2+'Operating Model'!$F$24/(1+$B7)^3+'Operating Model'!$G$24/(1+$B7)^4+'Operating Model'!$H$24/(1+$B7)^5+'Operating Model'!$H$12*J$4/(1+$B7)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="39" t="n">
-        <v>0.09</v>
+      <c r="B8" s="22">
+        <f>Assumptions!$C$23+(0)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*C$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*C$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*D$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*D$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*E$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*E$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*F$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*F$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*G$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*G$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*H$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*H$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*I$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*I$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J8" s="13">
-        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*J$4/(1+$B8)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B8)^1+'Operating Model'!$E$24/(1+$B8)^2+'Operating Model'!$F$24/(1+$B8)^3+'Operating Model'!$G$24/(1+$B8)^4+'Operating Model'!$H$24/(1+$B8)^5+'Operating Model'!$H$12*J$4/(1+$B8)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="39" t="n">
-        <v>0.095</v>
+      <c r="B9" s="22">
+        <f>Assumptions!$C$23+(1)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*C$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*C$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*D$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*D$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*E$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*E$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*F$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*F$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*G$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*G$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*H$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*H$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*I$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*I$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J9" s="13">
-        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*J$4/(1+$B9)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B9)^1+'Operating Model'!$E$24/(1+$B9)^2+'Operating Model'!$F$24/(1+$B9)^3+'Operating Model'!$G$24/(1+$B9)^4+'Operating Model'!$H$24/(1+$B9)^5+'Operating Model'!$H$12*J$4/(1+$B9)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="39" t="n">
-        <v>0.1</v>
+      <c r="B10" s="22">
+        <f>Assumptions!$C$23+(2)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*C$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*C$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*D$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*D$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*E$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*E$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*F$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*F$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*G$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*G$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*H$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*H$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*I$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*I$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J10" s="13">
-        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*J$4/(1+$B10)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B10)^1+'Operating Model'!$E$24/(1+$B10)^2+'Operating Model'!$F$24/(1+$B10)^3+'Operating Model'!$G$24/(1+$B10)^4+'Operating Model'!$H$24/(1+$B10)^5+'Operating Model'!$H$12*J$4/(1+$B10)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="39" t="n">
-        <v>0.105</v>
+      <c r="B11" s="22">
+        <f>Assumptions!$C$23+(3)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*C$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*C$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*D$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*D$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*E$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*E$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*F$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*F$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*G$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*G$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*H$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*H$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*I$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*I$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J11" s="13">
-        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*J$4/(1+$B11)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B11)^1+'Operating Model'!$E$24/(1+$B11)^2+'Operating Model'!$F$24/(1+$B11)^3+'Operating Model'!$G$24/(1+$B11)^4+'Operating Model'!$H$24/(1+$B11)^5+'Operating Model'!$H$12*J$4/(1+$B11)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="39" t="n">
-        <v>0.11</v>
+      <c r="B12" s="22">
+        <f>Assumptions!$C$23+(4)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*C$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*C$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*D$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*D$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*E$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*E$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*F$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*F$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*G$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*G$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*H$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*H$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*I$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*I$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J12" s="13">
-        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*J$4/(1+$B12)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+$B12)^1+'Operating Model'!$E$24/(1+$B12)^2+'Operating Model'!$F$24/(1+$B12)^3+'Operating Model'!$G$24/(1+$B12)^4+'Operating Model'!$H$24/(1+$B12)^5+'Operating Model'!$H$12*J$4/(1+$B12)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t>★ Base case: WACC 9.0%, 16× exit multiple. Formulas reference live Operating Model and Assumptions — update assumptions to refresh.</t>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>★ Base case = 4th row / 4th column (base WACC × base exit multiple). Axes, cash, convertible debt and shares all link to Assumptions.</t>
         </is>
       </c>
     </row>
@@ -3069,336 +3314,352 @@
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>WACC ↓ | QNX EV/Rev →</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="38" t="n">
-        <v>6</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="H18" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="I18" s="38" t="n">
-        <v>11</v>
-      </c>
-      <c r="J18" s="38" t="n">
-        <v>12</v>
+      <c r="C18" s="40">
+        <f>Assumptions!$C$29+(-3)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
+        <f>Assumptions!$C$29+(-2)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="E18" s="40">
+        <f>Assumptions!$C$29+(-1)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="F18" s="40">
+        <f>Assumptions!$C$29+(0)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="G18" s="40">
+        <f>Assumptions!$C$29+(1)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="H18" s="40">
+        <f>Assumptions!$C$29+(2)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="I18" s="40">
+        <f>Assumptions!$C$29+(3)*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="J18" s="40">
+        <f>Assumptions!$C$29+(4)*Assumptions!$C$52</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="39" t="n">
-        <v>0.075</v>
+      <c r="B19" s="22">
+        <f>Assumptions!$C$23+(-3)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J19" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B19)^1+'Operating Model'!$E$24/(1+$B19)^2+'Operating Model'!$F$24/(1+$B19)^3+'Operating Model'!$G$24/(1+$B19)^4+'Operating Model'!$H$24/(1+$B19)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B19)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="39" t="n">
-        <v>0.08</v>
+      <c r="B20" s="22">
+        <f>Assumptions!$C$23+(-2)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J20" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B20)^1+'Operating Model'!$E$24/(1+$B20)^2+'Operating Model'!$F$24/(1+$B20)^3+'Operating Model'!$G$24/(1+$B20)^4+'Operating Model'!$H$24/(1+$B20)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B20)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="39" t="n">
-        <v>0.08500000000000001</v>
+      <c r="B21" s="22">
+        <f>Assumptions!$C$23+(-1)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J21" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B21)^1+'Operating Model'!$E$24/(1+$B21)^2+'Operating Model'!$F$24/(1+$B21)^3+'Operating Model'!$G$24/(1+$B21)^4+'Operating Model'!$H$24/(1+$B21)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B21)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="39" t="n">
-        <v>0.09</v>
+      <c r="B22" s="22">
+        <f>Assumptions!$C$23+(0)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J22" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B22)^1+'Operating Model'!$E$24/(1+$B22)^2+'Operating Model'!$F$24/(1+$B22)^3+'Operating Model'!$G$24/(1+$B22)^4+'Operating Model'!$H$24/(1+$B22)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B22)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="39" t="n">
-        <v>0.095</v>
+      <c r="B23" s="22">
+        <f>Assumptions!$C$23+(1)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B23)^1+'Operating Model'!$E$24/(1+$B23)^2+'Operating Model'!$F$24/(1+$B23)^3+'Operating Model'!$G$24/(1+$B23)^4+'Operating Model'!$H$24/(1+$B23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="39" t="n">
-        <v>0.1</v>
+      <c r="B24" s="22">
+        <f>Assumptions!$C$23+(2)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J24" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B24)^1+'Operating Model'!$E$24/(1+$B24)^2+'Operating Model'!$F$24/(1+$B24)^3+'Operating Model'!$G$24/(1+$B24)^4+'Operating Model'!$H$24/(1+$B24)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="39" t="n">
-        <v>0.105</v>
+      <c r="B25" s="22">
+        <f>Assumptions!$C$23+(3)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J25" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B25)^1+'Operating Model'!$E$24/(1+$B25)^2+'Operating Model'!$F$24/(1+$B25)^3+'Operating Model'!$G$24/(1+$B25)^4+'Operating Model'!$H$24/(1+$B25)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="39" t="n">
-        <v>0.11</v>
+      <c r="B26" s="22">
+        <f>Assumptions!$C$23+(4)*Assumptions!$C$50</f>
+        <v/>
       </c>
       <c r="C26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*C$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*D$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*E$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="F26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*F$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*G$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*H$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*I$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="J26" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+$B26)^1+'Operating Model'!$E$24/(1+$B26)^2+'Operating Model'!$F$24/(1+$B26)^3+'Operating Model'!$G$24/(1+$B26)^4+'Operating Model'!$H$24/(1+$B26)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+$B26)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*J$18+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="40" t="inlineStr">
-        <is>
-          <t>Blended PT = 40% DCF + 60% Comps. QNX multiple varies by column; CySec multiple held at Assumptions!$C$30. All formulas live.</t>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>Blended PT = DCF weight × DCF + comps weight × comps (discounted FY2028E segment EV). QNX multiple varies by column; CySec multiple held at Assumptions. All formulas live.</t>
         </is>
       </c>
     </row>
@@ -3461,29 +3722,28 @@
         <f>Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="42">
         <f>Assumptions!$C$28</f>
         <v/>
       </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>6.0x</t>
-        </is>
+      <c r="E33" s="42">
+        <f>Assumptions!$C$46</f>
+        <v/>
       </c>
       <c r="F33" s="13">
-        <f>('Operating Model'!$D$24/(1+Assumptions!$C$25)^1+'Operating Model'!$E$24/(1+Assumptions!$C$25)^2+'Operating Model'!$F$24/(1+Assumptions!$C$25)^3+'Operating Model'!$G$24/(1+Assumptions!$C$25)^4+'Operating Model'!$H$24/(1+Assumptions!$C$25)^5+'Operating Model'!$H$12*Assumptions!$C$28/(1+Assumptions!$C$25)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+Assumptions!$C$25)^1+'Operating Model'!$E$24/(1+Assumptions!$C$25)^2+'Operating Model'!$F$24/(1+Assumptions!$C$25)^3+'Operating Model'!$G$24/(1+Assumptions!$C$25)^4+'Operating Model'!$H$24/(1+Assumptions!$C$25)^5+'Operating Model'!$H$12*Assumptions!$C$28/(1+Assumptions!$C$25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G33" s="13">
-        <f>('Operating Model'!$E$4*6.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>(('Operating Model'!$E$4*Assumptions!$C$46+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H33" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$25)^1+'Operating Model'!$E$24/(1+Assumptions!$C$25)^2+'Operating Model'!$F$24/(1+Assumptions!$C$25)^3+'Operating Model'!$G$24/(1+Assumptions!$C$25)^4+'Operating Model'!$H$24/(1+Assumptions!$C$25)^5+'Operating Model'!$H$12*Assumptions!$C$28/(1+Assumptions!$C$25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*6.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$25)^1+'Operating Model'!$E$24/(1+Assumptions!$C$25)^2+'Operating Model'!$F$24/(1+Assumptions!$C$25)^3+'Operating Model'!$G$24/(1+Assumptions!$C$25)^4+'Operating Model'!$H$24/(1+Assumptions!$C$25)^5+'Operating Model'!$H$12*Assumptions!$C$28/(1+Assumptions!$C$25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*Assumptions!$C$46+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I33" s="14">
-        <f>(Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$25)^1+'Operating Model'!$E$24/(1+Assumptions!$C$25)^2+'Operating Model'!$F$24/(1+Assumptions!$C$25)^3+'Operating Model'!$G$24/(1+Assumptions!$C$25)^4+'Operating Model'!$H$24/(1+Assumptions!$C$25)^5+'Operating Model'!$H$12*Assumptions!$C$28/(1+Assumptions!$C$25)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*6.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42-Assumptions!$C$43)/Assumptions!$C$43</f>
+        <f>(Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$25)^1+'Operating Model'!$E$24/(1+Assumptions!$C$25)^2+'Operating Model'!$F$24/(1+Assumptions!$C$25)^3+'Operating Model'!$G$24/(1+Assumptions!$C$25)^4+'Operating Model'!$H$24/(1+Assumptions!$C$25)^5+'Operating Model'!$H$12*Assumptions!$C$28/(1+Assumptions!$C$25)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*Assumptions!$C$46+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42-Assumptions!$C$43)/Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -3493,33 +3753,32 @@
           <t>Base ★</t>
         </is>
       </c>
-      <c r="C34" s="42">
+      <c r="C34" s="43">
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="44">
         <f>Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="E34" s="44" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
+      <c r="E34" s="44">
+        <f>Assumptions!$C$29</f>
+        <v/>
       </c>
       <c r="F34" s="45">
-        <f>('Operating Model'!$D$24/(1+Assumptions!$C$23)^1+'Operating Model'!$E$24/(1+Assumptions!$C$23)^2+'Operating Model'!$F$24/(1+Assumptions!$C$23)^3+'Operating Model'!$G$24/(1+Assumptions!$C$23)^4+'Operating Model'!$H$24/(1+Assumptions!$C$23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+Assumptions!$C$23)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+Assumptions!$C$23)^1+'Operating Model'!$E$24/(1+Assumptions!$C$23)^2+'Operating Model'!$F$24/(1+Assumptions!$C$23)^3+'Operating Model'!$G$24/(1+Assumptions!$C$23)^4+'Operating Model'!$H$24/(1+Assumptions!$C$23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+Assumptions!$C$23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G34" s="45">
-        <f>('Operating Model'!$E$4*8.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>(('Operating Model'!$E$4*Assumptions!$C$29+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H34" s="45">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$23)^1+'Operating Model'!$E$24/(1+Assumptions!$C$23)^2+'Operating Model'!$F$24/(1+Assumptions!$C$23)^3+'Operating Model'!$G$24/(1+Assumptions!$C$23)^4+'Operating Model'!$H$24/(1+Assumptions!$C$23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+Assumptions!$C$23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*8.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
-        <v/>
-      </c>
-      <c r="I34" s="42">
-        <f>(Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$23)^1+'Operating Model'!$E$24/(1+Assumptions!$C$23)^2+'Operating Model'!$F$24/(1+Assumptions!$C$23)^3+'Operating Model'!$G$24/(1+Assumptions!$C$23)^4+'Operating Model'!$H$24/(1+Assumptions!$C$23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+Assumptions!$C$23)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*8.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42-Assumptions!$C$43)/Assumptions!$C$43</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$23)^1+'Operating Model'!$E$24/(1+Assumptions!$C$23)^2+'Operating Model'!$F$24/(1+Assumptions!$C$23)^3+'Operating Model'!$G$24/(1+Assumptions!$C$23)^4+'Operating Model'!$H$24/(1+Assumptions!$C$23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+Assumptions!$C$23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*Assumptions!$C$29+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
+        <v/>
+      </c>
+      <c r="I34" s="43">
+        <f>(Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$23)^1+'Operating Model'!$E$24/(1+Assumptions!$C$23)^2+'Operating Model'!$F$24/(1+Assumptions!$C$23)^3+'Operating Model'!$G$24/(1+Assumptions!$C$23)^4+'Operating Model'!$H$24/(1+Assumptions!$C$23)^5+'Operating Model'!$H$12*Assumptions!$C$26/(1+Assumptions!$C$23)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*Assumptions!$C$29+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42-Assumptions!$C$43)/Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -3533,29 +3792,28 @@
         <f>Assumptions!$C$24</f>
         <v/>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="42">
         <f>Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>10.0x</t>
-        </is>
+      <c r="E35" s="42">
+        <f>Assumptions!$C$47</f>
+        <v/>
       </c>
       <c r="F35" s="13">
-        <f>('Operating Model'!$D$24/(1+Assumptions!$C$24)^1+'Operating Model'!$E$24/(1+Assumptions!$C$24)^2+'Operating Model'!$F$24/(1+Assumptions!$C$24)^3+'Operating Model'!$G$24/(1+Assumptions!$C$24)^4+'Operating Model'!$H$24/(1+Assumptions!$C$24)^5+'Operating Model'!$H$12*Assumptions!$C$27/(1+Assumptions!$C$24)^5+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>('Operating Model'!$D$24/(1+Assumptions!$C$24)^1+'Operating Model'!$E$24/(1+Assumptions!$C$24)^2+'Operating Model'!$F$24/(1+Assumptions!$C$24)^3+'Operating Model'!$G$24/(1+Assumptions!$C$24)^4+'Operating Model'!$H$24/(1+Assumptions!$C$24)^5+'Operating Model'!$H$12*Assumptions!$C$27/(1+Assumptions!$C$24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="G35" s="13">
-        <f>('Operating Model'!$E$4*10.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>(('Operating Model'!$E$4*Assumptions!$C$47+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="H35" s="13">
-        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$24)^1+'Operating Model'!$E$24/(1+Assumptions!$C$24)^2+'Operating Model'!$F$24/(1+Assumptions!$C$24)^3+'Operating Model'!$G$24/(1+Assumptions!$C$24)^4+'Operating Model'!$H$24/(1+Assumptions!$C$24)^5+'Operating Model'!$H$12*Assumptions!$C$27/(1+Assumptions!$C$24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*10.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42</f>
+        <f>Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$24)^1+'Operating Model'!$E$24/(1+Assumptions!$C$24)^2+'Operating Model'!$F$24/(1+Assumptions!$C$24)^3+'Operating Model'!$G$24/(1+Assumptions!$C$24)^4+'Operating Model'!$H$24/(1+Assumptions!$C$24)^5+'Operating Model'!$H$12*Assumptions!$C$27/(1+Assumptions!$C$24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*Assumptions!$C$47+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="I35" s="14">
-        <f>(Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$24)^1+'Operating Model'!$E$24/(1+Assumptions!$C$24)^2+'Operating Model'!$F$24/(1+Assumptions!$C$24)^3+'Operating Model'!$G$24/(1+Assumptions!$C$24)^4+'Operating Model'!$H$24/(1+Assumptions!$C$24)^5+'Operating Model'!$H$12*Assumptions!$C$27/(1+Assumptions!$C$24)^5+Assumptions!$C$41)/Assumptions!$C$42+Assumptions!$C$32*('Operating Model'!$E$4*10.0+'Operating Model'!$E$6*Assumptions!$C$30+Assumptions!$C$41)/Assumptions!$C$42-Assumptions!$C$43)/Assumptions!$C$43</f>
+        <f>(Assumptions!$C$31*('Operating Model'!$D$24/(1+Assumptions!$C$24)^1+'Operating Model'!$E$24/(1+Assumptions!$C$24)^2+'Operating Model'!$F$24/(1+Assumptions!$C$24)^3+'Operating Model'!$G$24/(1+Assumptions!$C$24)^4+'Operating Model'!$H$24/(1+Assumptions!$C$24)^5+'Operating Model'!$H$12*Assumptions!$C$27/(1+Assumptions!$C$24)^5+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42+Assumptions!$C$32*(('Operating Model'!$E$4*Assumptions!$C$47+'Operating Model'!$E$6*Assumptions!$C$30)/(1+Assumptions!$C$23)^Assumptions!$C$45+Assumptions!$C$41-Assumptions!$C$44)/Assumptions!$C$42-Assumptions!$C$43)/Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
